--- a/demo_data/ward_patients.xlsx
+++ b/demo_data/ward_patients.xlsx
@@ -496,30 +496,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Suresh Rao</t>
+          <t>Vikram Pillai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ward 3A</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Osteoarthritis</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -527,14 +527,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BP 114/90, HR 73, SpO2 93%</t>
+          <t>BP 136/81, HR 82, SpO2 99%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -553,7 +553,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vikram Dutta</t>
+          <t>Anil Bose</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -566,35 +566,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BP 126/62, HR 61, SpO2 96%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>BP 113/74, HR 95, SpO2 99%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -610,48 +610,48 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pooja Agarwal</t>
+          <t>Pooja Malhotra</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ward HDU</t>
+          <t>Ward 3A</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>BP 148/77, HR 91, SpO2 95%</t>
+          <t>BP 149/73, HR 98, SpO2 92%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -667,48 +667,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanjay Nair</t>
+          <t>Anil Joshi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ward ICU</t>
+          <t>Ward 3A</t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dr. Priya Mehta</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CKD Stage 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BP 108/73, HR 74, SpO2 100%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dr. Manish Gupta</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>COPD</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>BP 135/89, HR 81, SpO2 94%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -724,7 +724,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meena Rao</t>
+          <t>Suresh Singh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -733,21 +733,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -755,17 +755,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BP 144/76, HR 69, SpO2 93%</t>
+          <t>BP 117/72, HR 99, SpO2 98%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -781,45 +781,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kavita Patel</t>
+          <t>Pooja Mehta</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ward ICU</t>
+          <t>Ward 3B</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypothyroidism</t>
+          <t>Schizophrenia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BP 112/86, HR 96, SpO2 92%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="n">
         <v>4</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>BP 125/68, HR 80, SpO2 92%</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>5</v>
@@ -838,45 +838,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee</t>
+          <t>Pooja Verma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ward 3A</t>
+          <t>Ward 3B</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BP 100/88, HR 81, SpO2 92%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>BP 113/69, HR 96, SpO2 93%</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
@@ -895,16 +895,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arjun Pillai</t>
+          <t>Kiran Iyer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ward HDU</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -913,30 +913,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Breast Cancer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BP 100/87, HR 61, SpO2 96%</t>
+          <t>BP 100/61, HR 87, SpO2 95%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -952,48 +952,48 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manish Nair</t>
+          <t>Usha Kumar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ward 3A</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BP 134/64, HR 64, SpO2 97%</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>BP 103/78, HR 77, SpO2 92%</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1009,45 +1009,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anil Sharma</t>
+          <t>Kavita Mehta</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ward 2A</t>
+          <t>Ward ICU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BP 145/80, HR 65, SpO2 96%</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>BP 131/73, HR 84, SpO2 98%</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1066,16 +1066,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Usha Bose</t>
+          <t>Pooja Chatterjee</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ward 3B</t>
+          <t>Ward ICU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BP 116/68, HR 88, SpO2 97%</t>
+          <t>BP 104/66, HR 60, SpO2 95%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1123,30 +1123,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anita Sharma</t>
+          <t>Kiran Kumar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ward ICU</t>
+          <t>Ward HDU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dr. Sunita Sharma</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BP 147/61, HR 100, SpO2 95%</t>
+          <t>BP 138/74, HR 89, SpO2 96%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
         <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1180,48 +1180,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>Amit Kapoor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ward 3A</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Schizophrenia</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BP 121/77, HR 79, SpO2 92%</t>
+          <t>BP 104/75, HR 72, SpO2 100%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Anita Shah</t>
+          <t>Anita Bose</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ward HDU</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1250,35 +1250,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BP 105/75, HR 89, SpO2 97%</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>BP 132/80, HR 96, SpO2 92%</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1294,48 +1294,48 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Usha Iyer</t>
+          <t>Meena Dutta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ward HDU</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CKD Stage 3</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>BP 122/81, HR 66, SpO2 94%</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>BP 142/88, HR 90, SpO2 93%</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manish Singh</t>
+          <t>Priya Iyer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1360,39 +1360,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Schizophrenia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BP 122/89, HR 61, SpO2 94%</t>
+          <t>BP 103/64, HR 61, SpO2 92%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1408,38 +1408,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Usha Iyer</t>
+          <t>Nisha Singh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ward ICU</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteoarthritis</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>BP 126/81, HR 60, SpO2 93%</t>
+          <t>BP 138/63, HR 72, SpO2 93%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1449,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1465,48 +1465,48 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rekha Chatterjee</t>
+          <t>Amit Rao</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ward HDU</t>
+          <t>Ward 2A</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BP 135/77, HR 60, SpO2 92%</t>
+          <t>BP 111/80, HR 90, SpO2 94%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1522,48 +1522,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vikram Mehta</t>
+          <t>Usha Kumar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ward HDU</t>
+          <t>Ward 3B</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BP 147/69, HR 87, SpO2 96%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>BP 126/88, HR 77, SpO2 100%</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
       <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1579,16 +1579,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pooja Sharma</t>
+          <t>Vikram Malhotra</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ward 2A</t>
+          <t>Ward 3B</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>BP 114/66, HR 83, SpO2 97%</t>
+          <t>BP 112/79, HR 97, SpO2 92%</t>
         </is>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
